--- a/output/tables/mesh/experiment_2/stats-level_glm_level0.xlsx
+++ b/output/tables/mesh/experiment_2/stats-level_glm_level0.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -385,6 +385,11 @@
           <t>mesh_term</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>stats.sign</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -393,20 +398,25 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.003370332528527029</v>
+        <v>-0.00789126670044186</v>
       </c>
       <c r="C2">
-        <v>0.01159483248851182</v>
+        <v>0.005151688918540836</v>
       </c>
       <c r="D2">
-        <v>0.2906753962910944</v>
+        <v>-1.531782455272354</v>
       </c>
       <c r="E2">
-        <v>0.7712995903950803</v>
+        <v>0.1255761269563748</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Organisms</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -417,20 +427,25 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.005158396154581428</v>
+        <v>-0.006088246845327528</v>
       </c>
       <c r="C3">
-        <v>0.01110261164902694</v>
+        <v>0.006481504745471424</v>
       </c>
       <c r="D3">
-        <v>0.4646110588794233</v>
+        <v>-0.9393261417545575</v>
       </c>
       <c r="E3">
-        <v>0.6422100113148779</v>
+        <v>0.3475633207392975</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Analytical, Diagnostic and Therapeutic Techniques, and Equipment</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -441,20 +456,25 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.0003200012814193329</v>
+        <v>-0.008298779293962184</v>
       </c>
       <c r="C4">
-        <v>0.01254317154518151</v>
+        <v>0.006781554809150541</v>
       </c>
       <c r="D4">
-        <v>0.02551199114726788</v>
+        <v>-1.223728116561767</v>
       </c>
       <c r="E4">
-        <v>0.9796465840486602</v>
+        <v>0.2210548093250752</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Health Care</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -465,20 +485,25 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.01618246622909271</v>
+        <v>0.001125743715287233</v>
       </c>
       <c r="C5">
-        <v>0.01342149179274542</v>
+        <v>0.007459963759376407</v>
       </c>
       <c r="D5">
-        <v>1.205712932584711</v>
+        <v>0.1509047163764421</v>
       </c>
       <c r="E5">
-        <v>0.227928196738651</v>
+        <v>0.8800508799659006</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Phenomena and Processes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -489,20 +514,25 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.01191806275939768</v>
+        <v>0.003216532824229183</v>
       </c>
       <c r="C6">
-        <v>0.01488104194446039</v>
+        <v>0.007989481986750147</v>
       </c>
       <c r="D6">
-        <v>0.8008889971467545</v>
+        <v>0.402595916676891</v>
       </c>
       <c r="E6">
-        <v>0.4231959104217797</v>
+        <v>0.6872455140610555</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>Information Science</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -513,20 +543,25 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.009881493612966903</v>
+        <v>-0.00570489414034002</v>
       </c>
       <c r="C7">
-        <v>0.01953068338674921</v>
+        <v>0.006063780981524574</v>
       </c>
       <c r="D7">
-        <v>0.5059471508135297</v>
+        <v>-0.9408146761438073</v>
       </c>
       <c r="E7">
-        <v>0.6128937507553968</v>
+        <v>0.3467998385984589</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Diseases</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -537,20 +572,25 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.01562432421494659</v>
+        <v>0.0004464322779452414</v>
       </c>
       <c r="C8">
-        <v>0.01548986811254355</v>
+        <v>0.00659727202452429</v>
       </c>
       <c r="D8">
-        <v>1.008680261279575</v>
+        <v>0.06766922392857255</v>
       </c>
       <c r="E8">
-        <v>0.3131280011653594</v>
+        <v>0.9460489488821552</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>Named Groups</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -561,20 +601,25 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.01894250237001701</v>
+        <v>-0.02394618991607016</v>
       </c>
       <c r="C9">
-        <v>0.01797789613815859</v>
+        <v>0.008092165762262717</v>
       </c>
       <c r="D9">
-        <v>-1.053655123182685</v>
+        <v>-2.95918183334079</v>
       </c>
       <c r="E9">
-        <v>0.2920408420467244</v>
+        <v>0.003084570370894043</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>Psychiatry and Psychology</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>**</t>
         </is>
       </c>
     </row>
@@ -585,20 +630,25 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.02363319396905329</v>
+        <v>0.0131956419735254</v>
       </c>
       <c r="C10">
-        <v>0.0178696601642707</v>
+        <v>0.007794645234987047</v>
       </c>
       <c r="D10">
-        <v>1.322531808204525</v>
+        <v>1.692911168592438</v>
       </c>
       <c r="E10">
-        <v>0.1859911246710405</v>
+        <v>0.09047237711414877</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Female</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -609,20 +659,25 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.0004792463800672887</v>
+        <v>0.000180976883612313</v>
       </c>
       <c r="C11">
-        <v>0.01784266917490315</v>
+        <v>0.007648477085105365</v>
       </c>
       <c r="D11">
-        <v>0.0268595676672288</v>
+        <v>0.02366181941824041</v>
       </c>
       <c r="E11">
-        <v>0.9785717422002249</v>
+        <v>0.981122361162864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>Anatomy</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -633,20 +688,25 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.004583367999737158</v>
+        <v>0.001880757629575273</v>
       </c>
       <c r="C12">
-        <v>0.01916512968752853</v>
+        <v>0.008551963756664069</v>
       </c>
       <c r="D12">
-        <v>0.2391514210686363</v>
+        <v>0.2199211412828666</v>
       </c>
       <c r="E12">
-        <v>0.8109881701042466</v>
+        <v>0.8259325709979959</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -657,20 +717,25 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.04947116379453476</v>
+        <v>0.003474909713100807</v>
       </c>
       <c r="C13">
-        <v>0.01814374156477375</v>
+        <v>0.009129990394998929</v>
       </c>
       <c r="D13">
-        <v>2.726624142981814</v>
+        <v>0.3806038739103421</v>
       </c>
       <c r="E13">
-        <v>0.006398587801210876</v>
+        <v>0.7034972063176569</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Chemicals and Drugs</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -681,20 +746,25 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.02298740775198724</v>
+        <v>-0.02492524911567974</v>
       </c>
       <c r="C14">
-        <v>0.01802859854868143</v>
+        <v>0.00914502209479133</v>
       </c>
       <c r="D14">
-        <v>-1.275052394667055</v>
+        <v>-2.725553733749451</v>
       </c>
       <c r="E14">
-        <v>0.2022906975967131</v>
+        <v>0.006419372660834593</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Disciplines and Occupations</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>**</t>
         </is>
       </c>
     </row>
@@ -705,20 +775,25 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.0598733329973585</v>
+        <v>-0.02390599997843999</v>
       </c>
       <c r="C15">
-        <v>0.02162995552393815</v>
+        <v>0.009188645456442863</v>
       </c>
       <c r="D15">
-        <v>-2.768074716154452</v>
+        <v>-2.60168923610799</v>
       </c>
       <c r="E15">
-        <v>0.005638852664635605</v>
+        <v>0.009276587011716787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>Anthropology, Education, Sociology, and Social Phenomena</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>**</t>
         </is>
       </c>
     </row>
@@ -729,20 +804,25 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.009795923921687431</v>
+        <v>-0.0156350052890929</v>
       </c>
       <c r="C16">
-        <v>0.02224732315120452</v>
+        <v>0.009043192300733081</v>
       </c>
       <c r="D16">
-        <v>-0.4403192175125598</v>
+        <v>-1.728925446805489</v>
       </c>
       <c r="E16">
-        <v>0.6597059239682541</v>
+        <v>0.08382243906084788</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>Geographicals</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -753,20 +833,25 @@
         </is>
       </c>
       <c r="B17">
-        <v>-0.01091807579264462</v>
+        <v>0.01389277944860561</v>
       </c>
       <c r="C17">
-        <v>0.02330838782862854</v>
+        <v>0.009857747718214491</v>
       </c>
       <c r="D17">
-        <v>-0.4684183167415161</v>
+        <v>1.409325927760908</v>
       </c>
       <c r="E17">
-        <v>0.6394854718594726</v>
+        <v>0.158738815542733</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>Technology, Industry, and Agriculture</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -777,20 +862,25 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.04443389108037731</v>
+        <v>-0.003405795530291891</v>
       </c>
       <c r="C18">
-        <v>0.04115101553043655</v>
+        <v>0.01490272147422838</v>
       </c>
       <c r="D18">
-        <v>1.079776294889069</v>
+        <v>-0.2285351394496375</v>
       </c>
       <c r="E18">
-        <v>0.2802418096628149</v>
+        <v>0.8192302414785021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>Humanities</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>ns</t>
         </is>
       </c>
     </row>

--- a/output/tables/mesh/experiment_2/stats-level_glm_level0.xlsx
+++ b/output/tables/mesh/experiment_2/stats-level_glm_level0.xlsx
@@ -398,16 +398,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.00789126670044186</v>
+        <v>0.003370332528527029</v>
       </c>
       <c r="C2">
-        <v>0.005151688918540836</v>
+        <v>0.01159483248851182</v>
       </c>
       <c r="D2">
-        <v>-1.531782455272354</v>
+        <v>0.2906753962910944</v>
       </c>
       <c r="E2">
-        <v>0.1255761269563748</v>
+        <v>0.7712995903950803</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -427,16 +427,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.006088246845327528</v>
+        <v>0.005158396154581428</v>
       </c>
       <c r="C3">
-        <v>0.006481504745471424</v>
+        <v>0.01110261164902694</v>
       </c>
       <c r="D3">
-        <v>-0.9393261417545575</v>
+        <v>0.4646110588794233</v>
       </c>
       <c r="E3">
-        <v>0.3475633207392975</v>
+        <v>0.6422100113148779</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -456,16 +456,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.008298779293962184</v>
+        <v>0.0003200012814193329</v>
       </c>
       <c r="C4">
-        <v>0.006781554809150541</v>
+        <v>0.01254317154518151</v>
       </c>
       <c r="D4">
-        <v>-1.223728116561767</v>
+        <v>0.02551199114726788</v>
       </c>
       <c r="E4">
-        <v>0.2210548093250752</v>
+        <v>0.9796465840486602</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -485,16 +485,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.001125743715287233</v>
+        <v>0.01618246622909271</v>
       </c>
       <c r="C5">
-        <v>0.007459963759376407</v>
+        <v>0.01342149179274542</v>
       </c>
       <c r="D5">
-        <v>0.1509047163764421</v>
+        <v>1.205712932584711</v>
       </c>
       <c r="E5">
-        <v>0.8800508799659006</v>
+        <v>0.227928196738651</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.003216532824229183</v>
+        <v>0.01191806275939768</v>
       </c>
       <c r="C6">
-        <v>0.007989481986750147</v>
+        <v>0.01488104194446039</v>
       </c>
       <c r="D6">
-        <v>0.402595916676891</v>
+        <v>0.8008889971467545</v>
       </c>
       <c r="E6">
-        <v>0.6872455140610555</v>
+        <v>0.4231959104217797</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -543,16 +543,16 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.00570489414034002</v>
+        <v>0.009881493612966903</v>
       </c>
       <c r="C7">
-        <v>0.006063780981524574</v>
+        <v>0.01953068338674921</v>
       </c>
       <c r="D7">
-        <v>-0.9408146761438073</v>
+        <v>0.5059471508135297</v>
       </c>
       <c r="E7">
-        <v>0.3467998385984589</v>
+        <v>0.6128937507553968</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -572,16 +572,16 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.0004464322779452414</v>
+        <v>0.01562432421494659</v>
       </c>
       <c r="C8">
-        <v>0.00659727202452429</v>
+        <v>0.01548986811254355</v>
       </c>
       <c r="D8">
-        <v>0.06766922392857255</v>
+        <v>1.008680261279575</v>
       </c>
       <c r="E8">
-        <v>0.9460489488821552</v>
+        <v>0.3131280011653594</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -601,16 +601,16 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.02394618991607016</v>
+        <v>-0.01894250237001701</v>
       </c>
       <c r="C9">
-        <v>0.008092165762262717</v>
+        <v>0.01797789613815859</v>
       </c>
       <c r="D9">
-        <v>-2.95918183334079</v>
+        <v>-1.053655123182685</v>
       </c>
       <c r="E9">
-        <v>0.003084570370894043</v>
+        <v>0.2920408420467244</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -619,7 +619,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -630,16 +630,16 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.0131956419735254</v>
+        <v>0.02363319396905329</v>
       </c>
       <c r="C10">
-        <v>0.007794645234987047</v>
+        <v>0.0178696601642707</v>
       </c>
       <c r="D10">
-        <v>1.692911168592438</v>
+        <v>1.322531808204525</v>
       </c>
       <c r="E10">
-        <v>0.09047237711414877</v>
+        <v>0.1859911246710405</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.000180976883612313</v>
+        <v>0.0004792463800672887</v>
       </c>
       <c r="C11">
-        <v>0.007648477085105365</v>
+        <v>0.01784266917490315</v>
       </c>
       <c r="D11">
-        <v>0.02366181941824041</v>
+        <v>0.0268595676672288</v>
       </c>
       <c r="E11">
-        <v>0.981122361162864</v>
+        <v>0.9785717422002249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -688,16 +688,16 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.001880757629575273</v>
+        <v>0.004583367999737158</v>
       </c>
       <c r="C12">
-        <v>0.008551963756664069</v>
+        <v>0.01916512968752853</v>
       </c>
       <c r="D12">
-        <v>0.2199211412828666</v>
+        <v>0.2391514210686363</v>
       </c>
       <c r="E12">
-        <v>0.8259325709979959</v>
+        <v>0.8109881701042466</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -717,16 +717,16 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.003474909713100807</v>
+        <v>0.04947116379453476</v>
       </c>
       <c r="C13">
-        <v>0.009129990394998929</v>
+        <v>0.01814374156477375</v>
       </c>
       <c r="D13">
-        <v>0.3806038739103421</v>
+        <v>2.726624142981814</v>
       </c>
       <c r="E13">
-        <v>0.7034972063176569</v>
+        <v>0.006398587801210876</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ns</t>
+          <t>**</t>
         </is>
       </c>
     </row>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.02492524911567974</v>
+        <v>-0.02298740775198724</v>
       </c>
       <c r="C14">
-        <v>0.00914502209479133</v>
+        <v>0.01802859854868143</v>
       </c>
       <c r="D14">
-        <v>-2.725553733749451</v>
+        <v>-1.275052394667055</v>
       </c>
       <c r="E14">
-        <v>0.006419372660834593</v>
+        <v>0.2022906975967131</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>**</t>
+          <t>ns</t>
         </is>
       </c>
     </row>
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.02390599997843999</v>
+        <v>-0.0598733329973585</v>
       </c>
       <c r="C15">
-        <v>0.009188645456442863</v>
+        <v>0.02162995552393815</v>
       </c>
       <c r="D15">
-        <v>-2.60168923610799</v>
+        <v>-2.768074716154452</v>
       </c>
       <c r="E15">
-        <v>0.009276587011716787</v>
+        <v>0.005638852664635605</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -804,16 +804,16 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.0156350052890929</v>
+        <v>-0.009795923921687431</v>
       </c>
       <c r="C16">
-        <v>0.009043192300733081</v>
+        <v>0.02224732315120452</v>
       </c>
       <c r="D16">
-        <v>-1.728925446805489</v>
+        <v>-0.4403192175125598</v>
       </c>
       <c r="E16">
-        <v>0.08382243906084788</v>
+        <v>0.6597059239682541</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -833,16 +833,16 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.01389277944860561</v>
+        <v>-0.01091807579264462</v>
       </c>
       <c r="C17">
-        <v>0.009857747718214491</v>
+        <v>0.02330838782862854</v>
       </c>
       <c r="D17">
-        <v>1.409325927760908</v>
+        <v>-0.4684183167415161</v>
       </c>
       <c r="E17">
-        <v>0.158738815542733</v>
+        <v>0.6394854718594726</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -862,16 +862,16 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.003405795530291891</v>
+        <v>0.04443389108037731</v>
       </c>
       <c r="C18">
-        <v>0.01490272147422838</v>
+        <v>0.04115101553043655</v>
       </c>
       <c r="D18">
-        <v>-0.2285351394496375</v>
+        <v>1.079776294889069</v>
       </c>
       <c r="E18">
-        <v>0.8192302414785021</v>
+        <v>0.2802418096628149</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
